--- a/test/excel/win/parts/struct-held/copy-b2-d6.xlsx
+++ b/test/excel/win/parts/struct-held/copy-b2-d6.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-struct-held-45796-1\out\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-struct-held-30311-1\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB27D227-2F93-46A3-AB0F-A237E9CF608A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D2E98F1-45E4-47B0-850F-729428957F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{46E27979-23F9-46EF-8DD6-19CFEED2E58B}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{85403236-992E-433C-8F90-38934448D7D8}">
       <text>
         <r>
           <rPr>
@@ -70,7 +70,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{F4CA328D-E5D1-4286-B92D-607B39B532D6}">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{02F797AF-BA5D-4796-8308-14A452DBD5BE}">
       <text>
         <r>
           <rPr>
@@ -569,9 +569,9 @@
     <hyperlink ref="B3" r:id="rId1" tooltip="B3" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C5" location="S!A1" display="to A1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="D6" location="'T'!A1" display="to T" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F11" r:id="rId2" tooltip="B3" xr:uid="{775AFE10-3430-446F-8CB6-D87B920366D8}"/>
-    <hyperlink ref="G13" location="S!A1" display="to A1" xr:uid="{311D23AC-825F-4F31-83EE-706EA6D6DE37}"/>
-    <hyperlink ref="H14" location="'T'!A1" display="to T" xr:uid="{AB32EB76-6DBD-48F2-9926-8F854CDB84BE}"/>
+    <hyperlink ref="F11" r:id="rId2" tooltip="B3" xr:uid="{F3B44800-BB94-4F65-B46E-CBA8D34741ED}"/>
+    <hyperlink ref="G13" location="S!A1" display="to A1" xr:uid="{B7EB990B-1ABA-4771-987F-F9F161CDCDC9}"/>
+    <hyperlink ref="H14" location="'T'!A1" display="to T" xr:uid="{DC5E1F89-FDBB-4D0D-9F84-0989DB2CC631}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
